--- a/output/pdf_financials_xlsx/ALEN.U.xlsx
+++ b/output/pdf_financials_xlsx/ALEN.U.xlsx
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.364294</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -2676,7 +2676,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.364294</v>
       </c>

--- a/output/pdf_financials_xlsx/ALEN.U.xlsx
+++ b/output/pdf_financials_xlsx/ALEN.U.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.008810999999999999</v>
+        <v>0.364916</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.008269</v>
+        <v>0.340795</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.212518</v>
+        <v>-0.143587</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.010574</v>
+        <v>-0.321952</v>
       </c>
     </row>
     <row r="12">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001739</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005330000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.127248</v>
+        <v>-0.128987</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.321419</v>
+        <v>-0.321952</v>
       </c>
     </row>
     <row r="28">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.127248</v>
+        <v>-0.128987</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.321419</v>
+        <v>-0.321952</v>
       </c>
     </row>
     <row r="30">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-51.81128587657116</v>
+        <v>-52.51935064882186</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-112.608301130571</v>
+        <v>-112.7950362784701</v>
       </c>
     </row>
     <row r="31">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.030658</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.050819</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.030658</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.050819</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.158464</v>
+        <v>0.127806</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.07334499999999999</v>
+        <v>0.022526</v>
       </c>
     </row>
     <row r="49">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALEN.U.xlsx
+++ b/output/pdf_financials_xlsx/ALEN.U.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.008810999999999999</v>
+        <v>0.020811</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.008269</v>
+        <v>0.028269</v>
       </c>
     </row>
     <row r="8">
@@ -3552,7 +3552,11 @@
           <t>Director’s fee (Note 12)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.012</v>
       </c>
